--- a/StructureDefinition-openimis-contract.xlsx
+++ b/StructureDefinition-openimis-contract.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8904,7 +8904,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>22</v>
@@ -9017,7 +9017,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>22</v>
@@ -9241,7 +9241,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>22</v>
@@ -9352,7 +9352,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>22</v>
@@ -9461,7 +9461,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>22</v>
@@ -9570,7 +9570,7 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>22</v>
@@ -9792,7 +9792,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>22</v>
@@ -9903,7 +9903,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>22</v>
@@ -10236,7 +10236,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>22</v>
@@ -10347,7 +10347,7 @@
         <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>22</v>
@@ -10456,7 +10456,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>22</v>
@@ -10569,7 +10569,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>22</v>
@@ -10678,7 +10678,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>22</v>
@@ -10787,7 +10787,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>22</v>
@@ -11112,7 +11112,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>22</v>
@@ -11225,7 +11225,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -11334,7 +11334,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>22</v>
@@ -11443,7 +11443,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>22</v>
@@ -12981,7 +12981,7 @@
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -13090,7 +13090,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>22</v>
@@ -13199,7 +13199,7 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>22</v>
@@ -13308,7 +13308,7 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>22</v>
@@ -13417,7 +13417,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>22</v>
@@ -13526,7 +13526,7 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>22</v>
@@ -13635,7 +13635,7 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>22</v>
@@ -13744,7 +13744,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>22</v>
@@ -15068,7 +15068,7 @@
         <v>78</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>22</v>
@@ -15837,7 +15837,7 @@
         <v>78</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>22</v>
@@ -15950,7 +15950,7 @@
         <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>22</v>
@@ -16059,7 +16059,7 @@
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>22</v>
@@ -16170,7 +16170,7 @@
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>22</v>
@@ -16279,7 +16279,7 @@
         <v>78</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>22</v>
@@ -16830,7 +16830,7 @@
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>22</v>
@@ -16939,7 +16939,7 @@
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>22</v>
@@ -17048,7 +17048,7 @@
         <v>78</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>22</v>
@@ -17706,7 +17706,7 @@
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>22</v>
@@ -17815,7 +17815,7 @@
         <v>78</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>22</v>
@@ -18033,7 +18033,7 @@
         <v>78</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>22</v>
@@ -18142,7 +18142,7 @@
         <v>78</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>22</v>
@@ -18251,7 +18251,7 @@
         <v>78</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>22</v>
@@ -19020,7 +19020,7 @@
         <v>78</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>
@@ -19129,7 +19129,7 @@
         <v>78</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>22</v>
@@ -20344,7 +20344,7 @@
         <v>78</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>22</v>
@@ -20453,7 +20453,7 @@
         <v>78</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>22</v>
@@ -20562,7 +20562,7 @@
         <v>78</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>22</v>
@@ -20574,7 +20574,7 @@
         <v>22</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="L157" t="s" s="2">
         <v>690</v>
@@ -20671,7 +20671,7 @@
         <v>78</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>22</v>
@@ -21331,7 +21331,7 @@
         <v>78</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>22</v>
@@ -21440,7 +21440,7 @@
         <v>78</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>22</v>
@@ -21549,7 +21549,7 @@
         <v>78</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>22</v>
@@ -21658,7 +21658,7 @@
         <v>78</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>22</v>
@@ -21767,7 +21767,7 @@
         <v>78</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>22</v>
@@ -21876,7 +21876,7 @@
         <v>78</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>22</v>
@@ -22538,7 +22538,7 @@
         <v>78</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>22</v>
@@ -22647,7 +22647,7 @@
         <v>78</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>22</v>
@@ -22756,7 +22756,7 @@
         <v>78</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>22</v>
@@ -22865,7 +22865,7 @@
         <v>78</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>22</v>
@@ -22974,7 +22974,7 @@
         <v>78</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>22</v>
@@ -23083,7 +23083,7 @@
         <v>78</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>22</v>
@@ -23192,7 +23192,7 @@
         <v>78</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>22</v>
@@ -26260,7 +26260,7 @@
         <v>78</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>22</v>
@@ -26272,7 +26272,7 @@
         <v>22</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="L209" t="s" s="2">
         <v>863</v>
@@ -26369,7 +26369,7 @@
         <v>78</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>22</v>
@@ -26478,7 +26478,7 @@
         <v>78</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>22</v>
@@ -26587,7 +26587,7 @@
         <v>78</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>22</v>
@@ -27360,7 +27360,7 @@
         <v>78</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>22</v>
@@ -27911,7 +27911,7 @@
         <v>78</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>22</v>
@@ -28462,7 +28462,7 @@
         <v>78</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>22</v>
@@ -29013,7 +29013,7 @@
         <v>78</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-contract.xlsx
+++ b/StructureDefinition-openimis-contract.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-contract.xlsx
+++ b/StructureDefinition-openimis-contract.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
